--- a/salidas/empresas/NEE.xlsx
+++ b/salidas/empresas/NEE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>5.649928569793701</v>
+        <v>5.649925708770752</v>
       </c>
       <c r="C2" t="n">
         <v>10.44750022888184</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>5.668851375579834</v>
+        <v>5.6688551902771</v>
       </c>
       <c r="C3" t="n">
         <v>10.48250007629395</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>5.476527214050293</v>
+        <v>5.476528167724609</v>
       </c>
       <c r="C4" t="n">
         <v>10.03499984741211</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>5.40285062789917</v>
+        <v>5.402852058410645</v>
       </c>
       <c r="C5" t="n">
         <v>9.899999618530273</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>5.43423318862915</v>
+        <v>5.434232711791992</v>
       </c>
       <c r="C6" t="n">
         <v>9.957500457763672</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>5.697668552398682</v>
+        <v>5.697667121887207</v>
       </c>
       <c r="C7" t="n">
         <v>10.34500026702881</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>5.940005779266357</v>
+        <v>5.940006256103516</v>
       </c>
       <c r="C8" t="n">
         <v>10.78499984741211</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>6.249372959136963</v>
+        <v>6.249371528625488</v>
       </c>
       <c r="C10" t="n">
         <v>11.25</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>7.082623958587646</v>
+        <v>7.082620620727539</v>
       </c>
       <c r="C11" t="n">
         <v>12.75</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>7.455054759979248</v>
+        <v>7.455053329467773</v>
       </c>
       <c r="C12" t="n">
         <v>13.32499980926514</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>7.611709594726562</v>
+        <v>7.611706733703613</v>
       </c>
       <c r="C13" t="n">
         <v>13.60499954223633</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>7.923616409301758</v>
+        <v>7.923617839813232</v>
       </c>
       <c r="C14" t="n">
         <v>14.16250038146973</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>8.323898315429688</v>
+        <v>8.323897361755371</v>
       </c>
       <c r="C15" t="n">
         <v>14.77499961853027</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>9.066147804260254</v>
+        <v>9.066149711608887</v>
       </c>
       <c r="C17" t="n">
         <v>16.09250068664551</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>9.004176139831543</v>
+        <v>9.004178047180176</v>
       </c>
       <c r="C18" t="n">
         <v>15.98250007629395</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>8.045282363891602</v>
+        <v>8.045281410217285</v>
       </c>
       <c r="C19" t="n">
         <v>14.1850004196167</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>8.185653686523438</v>
+        <v>8.18565559387207</v>
       </c>
       <c r="C20" t="n">
         <v>14.43249988555908</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>8.403212547302246</v>
+        <v>8.40321159362793</v>
       </c>
       <c r="C21" t="n">
         <v>14.71000003814697</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>8.694555282592773</v>
+        <v>8.694559097290039</v>
       </c>
       <c r="C22" t="n">
         <v>15.22000026702881</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>9.77137565612793</v>
+        <v>9.771376609802246</v>
       </c>
       <c r="C23" t="n">
         <v>17.10499954223633</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>10.02324104309082</v>
+        <v>10.02323627471924</v>
       </c>
       <c r="C24" t="n">
         <v>17.44000053405762</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>9.738746643066406</v>
+        <v>9.738747596740723</v>
       </c>
       <c r="C25" t="n">
         <v>16.94499969482422</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>9.24592113494873</v>
+        <v>9.245919227600098</v>
       </c>
       <c r="C26" t="n">
         <v>16.08749961853027</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>8.722424507141113</v>
+        <v>8.72242259979248</v>
       </c>
       <c r="C27" t="n">
         <v>15.07250022888184</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>9.076879501342773</v>
+        <v>9.076876640319824</v>
       </c>
       <c r="C28" t="n">
         <v>15.6850004196167</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>9.590473175048828</v>
+        <v>9.590471267700195</v>
       </c>
       <c r="C29" t="n">
         <v>16.57250022888184</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>9.768417358398438</v>
+        <v>9.768418312072754</v>
       </c>
       <c r="C30" t="n">
         <v>16.8799991607666</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>9.552343368530273</v>
+        <v>9.55234432220459</v>
       </c>
       <c r="C31" t="n">
         <v>16.39500045776367</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>9.399399757385254</v>
+        <v>9.399404525756836</v>
       </c>
       <c r="C32" t="n">
         <v>16.13249969482422</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>8.812770843505859</v>
+        <v>8.812769889831543</v>
       </c>
       <c r="C33" t="n">
         <v>15.01500034332275</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>7.380661487579346</v>
+        <v>7.380659580230713</v>
       </c>
       <c r="C34" t="n">
         <v>12.57499980926514</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>6.931658744812012</v>
+        <v>6.931660175323486</v>
       </c>
       <c r="C35" t="n">
         <v>11.8100004196167</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>7.45365047454834</v>
+        <v>7.453651905059814</v>
       </c>
       <c r="C37" t="n">
         <v>12.58250045776367</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>7.634326457977295</v>
+        <v>7.634324550628662</v>
       </c>
       <c r="C38" t="n">
         <v>12.88749980926514</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>6.778470993041992</v>
+        <v>6.778472423553467</v>
       </c>
       <c r="C39" t="n">
         <v>11.33250045776367</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>7.585966110229492</v>
+        <v>7.585970878601074</v>
       </c>
       <c r="C40" t="n">
         <v>12.68249988555908</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>8.043547630310059</v>
+        <v>8.043550491333008</v>
       </c>
       <c r="C41" t="n">
         <v>13.44750022888184</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>8.453278541564941</v>
+        <v>8.453275680541992</v>
       </c>
       <c r="C42" t="n">
         <v>14.13249969482422</v>
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>8.544268608093262</v>
+        <v>8.544266700744629</v>
       </c>
       <c r="C44" t="n">
         <v>14.16749954223633</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>8.540252685546875</v>
+        <v>8.540253639221191</v>
       </c>
       <c r="C45" t="n">
         <v>14.04500007629395</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>8.395837783813477</v>
+        <v>8.395835876464844</v>
       </c>
       <c r="C46" t="n">
         <v>13.80749988555908</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>7.463983058929443</v>
+        <v>7.463978290557861</v>
       </c>
       <c r="C47" t="n">
         <v>12.27499961853027</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>7.97277307510376</v>
+        <v>7.972771167755127</v>
       </c>
       <c r="C48" t="n">
         <v>12.99250030517578</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>8.103171348571777</v>
+        <v>8.10317325592041</v>
       </c>
       <c r="C49" t="n">
         <v>13.20499992370605</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.480322360992432</v>
+        <v>7.480321884155273</v>
       </c>
       <c r="C50" t="n">
         <v>12.1899995803833</v>
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>7.49442720413208</v>
+        <v>7.494425773620605</v>
       </c>
       <c r="C52" t="n">
         <v>12.08250045776367</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>8.071276664733887</v>
+        <v>8.07127571105957</v>
       </c>
       <c r="C53" t="n">
         <v>13.01249980926514</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.74253511428833</v>
+        <v>7.742534160614014</v>
       </c>
       <c r="C54" t="n">
         <v>12.48250007629395</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>7.639150142669678</v>
+        <v>7.639151573181152</v>
       </c>
       <c r="C55" t="n">
         <v>12.1899995803833</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>8.193756103515625</v>
+        <v>8.193757057189941</v>
       </c>
       <c r="C56" t="n">
         <v>13.07499980926514</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.496037483215332</v>
+        <v>8.496038436889648</v>
       </c>
       <c r="C57" t="n">
         <v>13.43249988555908</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>8.600404739379883</v>
+        <v>8.600399971008301</v>
       </c>
       <c r="C58" t="n">
         <v>13.59749984741211</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>8.703180313110352</v>
+        <v>8.703182220458984</v>
       </c>
       <c r="C59" t="n">
         <v>13.76000022888184</v>
@@ -1680,7 +1692,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>8.300578117370605</v>
+        <v>8.300576210021973</v>
       </c>
       <c r="C61" t="n">
         <v>12.9975004196167</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>8.535275459289551</v>
+        <v>8.535271644592285</v>
       </c>
       <c r="C62" t="n">
         <v>13.36499977111816</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>8.856183052062988</v>
+        <v>8.856184959411621</v>
       </c>
       <c r="C63" t="n">
         <v>13.86750030517578</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>8.890639305114746</v>
+        <v>8.890640258789062</v>
       </c>
       <c r="C64" t="n">
         <v>13.77999973297119</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>9.124518394470215</v>
+        <v>9.124519348144531</v>
       </c>
       <c r="C65" t="n">
         <v>14.14249992370605</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>9.347109794616699</v>
+        <v>9.347110748291016</v>
       </c>
       <c r="C66" t="n">
         <v>14.48750019073486</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>9.356878280639648</v>
+        <v>9.356881141662598</v>
       </c>
       <c r="C67" t="n">
         <v>14.36499977111816</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>8.997000694274902</v>
+        <v>8.996999740600586</v>
       </c>
       <c r="C68" t="n">
         <v>13.8125</v>
@@ -1929,7 +1941,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1958,7 +1970,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>9.276834487915039</v>
+        <v>9.276830673217773</v>
       </c>
       <c r="C71" t="n">
         <v>14.10000038146973</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>9.211553573608398</v>
+        <v>9.211551666259766</v>
       </c>
       <c r="C72" t="n">
         <v>13.85999965667725</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>10.11542320251465</v>
+        <v>10.11542701721191</v>
       </c>
       <c r="C73" t="n">
         <v>15.22000026702881</v>
@@ -2074,7 +2086,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>9.986872673034668</v>
+        <v>9.986867904663086</v>
       </c>
       <c r="C75" t="n">
         <v>14.8774995803833</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>10.25034332275391</v>
+        <v>10.25034713745117</v>
       </c>
       <c r="C76" t="n">
         <v>15.27000045776367</v>
@@ -2161,7 +2173,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>11.06714344024658</v>
+        <v>11.06714725494385</v>
       </c>
       <c r="C78" t="n">
         <v>16.33499908447266</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>11.65488719940186</v>
+        <v>11.65488624572754</v>
       </c>
       <c r="C79" t="n">
         <v>17.20249938964844</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>12.00888538360596</v>
+        <v>12.00888061523438</v>
       </c>
       <c r="C80" t="n">
         <v>17.72500038146973</v>
@@ -2277,7 +2289,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>12.01777648925781</v>
+        <v>12.0177755355835</v>
       </c>
       <c r="C82" t="n">
         <v>17.58250045776367</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>11.97164058685303</v>
+        <v>11.97163200378418</v>
       </c>
       <c r="C83" t="n">
         <v>17.51499938964844</v>
@@ -2364,7 +2376,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>11.92850685119629</v>
+        <v>11.92850589752197</v>
       </c>
       <c r="C85" t="n">
         <v>17.29750061035156</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>12.42157745361328</v>
+        <v>12.42157363891602</v>
       </c>
       <c r="C86" t="n">
         <v>18.01250076293945</v>
@@ -2451,7 +2463,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>13.51562881469727</v>
+        <v>13.51562786102295</v>
       </c>
       <c r="C88" t="n">
         <v>19.42000007629395</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>14.27249240875244</v>
+        <v>14.27248954772949</v>
       </c>
       <c r="C89" t="n">
         <v>20.50749969482422</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>13.27289581298828</v>
+        <v>13.2729024887085</v>
       </c>
       <c r="C90" t="n">
         <v>18.90500068664551</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>14.30145072937012</v>
+        <v>14.30145454406738</v>
       </c>
       <c r="C91" t="n">
         <v>20.3700008392334</v>
@@ -2596,7 +2608,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>14.22061729431152</v>
+        <v>14.22061061859131</v>
       </c>
       <c r="C93" t="n">
         <v>20.09000015258789</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>14.18521976470947</v>
+        <v>14.18521881103516</v>
       </c>
       <c r="C94" t="n">
         <v>20.04000091552734</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>14.99747657775879</v>
+        <v>14.99747753143311</v>
       </c>
       <c r="C95" t="n">
         <v>21.1875</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>15.08478927612305</v>
+        <v>15.08479404449463</v>
       </c>
       <c r="C96" t="n">
         <v>21.14749908447266</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>15.26846981048584</v>
+        <v>15.26846790313721</v>
       </c>
       <c r="C97" t="n">
         <v>21.40500068664551</v>
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2799,7 +2811,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2828,7 +2840,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>17.94808006286621</v>
+        <v>17.94807434082031</v>
       </c>
       <c r="C101" t="n">
         <v>24.96249961853027</v>
@@ -2886,7 +2898,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>18.55902671813965</v>
+        <v>18.55901908874512</v>
       </c>
       <c r="C103" t="n">
         <v>25.6200008392334</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>17.00338363647461</v>
+        <v>17.00337982177734</v>
       </c>
       <c r="C104" t="n">
         <v>23.47249984741211</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>17.96384429931641</v>
+        <v>17.96384811401367</v>
       </c>
       <c r="C105" t="n">
         <v>24.61249923706055</v>
@@ -3002,7 +3014,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>18.28681373596191</v>
+        <v>18.28680992126465</v>
       </c>
       <c r="C107" t="n">
         <v>25.05500030517578</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>19.18243408203125</v>
+        <v>19.18243980407715</v>
       </c>
       <c r="C108" t="n">
         <v>26.09749984741211</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>19.53157043457031</v>
+        <v>19.53157424926758</v>
       </c>
       <c r="C109" t="n">
         <v>26.57250022888184</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>20.07365417480469</v>
+        <v>20.07365036010742</v>
       </c>
       <c r="C110" t="n">
         <v>27.30999946594238</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>19.15054893493652</v>
+        <v>19.15054321289062</v>
       </c>
       <c r="C111" t="n">
         <v>25.86499977111816</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.25975227355957</v>
+        <v>19.25976181030273</v>
       </c>
       <c r="C112" t="n">
         <v>26.01250076293945</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>18.68224143981934</v>
+        <v>18.68223762512207</v>
       </c>
       <c r="C113" t="n">
         <v>25.23250007629395</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>19.08871841430664</v>
+        <v>19.08871269226074</v>
       </c>
       <c r="C114" t="n">
         <v>25.58499908447266</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>18.2848072052002</v>
+        <v>18.28480911254883</v>
       </c>
       <c r="C115" t="n">
         <v>24.50749969482422</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>19.62216949462891</v>
+        <v>19.62217140197754</v>
       </c>
       <c r="C116" t="n">
         <v>26.29999923706055</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>18.49739265441895</v>
+        <v>18.49739456176758</v>
       </c>
       <c r="C117" t="n">
         <v>24.60250091552734</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>18.33574104309082</v>
+        <v>18.33574867248535</v>
       </c>
       <c r="C118" t="n">
         <v>24.38750076293945</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>19.29623413085938</v>
+        <v>19.29623985290527</v>
       </c>
       <c r="C119" t="n">
         <v>25.66500091552734</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>18.91486740112305</v>
+        <v>18.91487121582031</v>
       </c>
       <c r="C120" t="n">
         <v>24.96500015258789</v>
@@ -3437,7 +3449,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>21.15942764282227</v>
+        <v>21.15942573547363</v>
       </c>
       <c r="C122" t="n">
         <v>27.92749977111816</v>
@@ -3495,7 +3507,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>22.58444976806641</v>
+        <v>22.58444786071777</v>
       </c>
       <c r="C124" t="n">
         <v>29.58499908447266</v>
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>23.09284782409668</v>
+        <v>23.09284400939941</v>
       </c>
       <c r="C126" t="n">
         <v>30.03000068664551</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>25.06915283203125</v>
+        <v>25.06915664672852</v>
       </c>
       <c r="C127" t="n">
         <v>32.59999847412109</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>24.66350364685059</v>
+        <v>24.66350555419922</v>
       </c>
       <c r="C128" t="n">
         <v>32.0724983215332</v>
@@ -3669,7 +3681,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>23.68125915527344</v>
+        <v>23.68125343322754</v>
       </c>
       <c r="C130" t="n">
         <v>30.57999992370605</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>24.78090286254883</v>
+        <v>24.78091239929199</v>
       </c>
       <c r="C131" t="n">
         <v>32</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>22.28457069396973</v>
+        <v>22.28456878662109</v>
       </c>
       <c r="C132" t="n">
         <v>28.5575008392334</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>23.30486679077148</v>
+        <v>23.30486488342285</v>
       </c>
       <c r="C133" t="n">
         <v>29.86499977111816</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>24.13592720031738</v>
+        <v>24.13592910766602</v>
       </c>
       <c r="C134" t="n">
         <v>30.93000030517578</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>25.75212478637695</v>
+        <v>25.75212669372559</v>
       </c>
       <c r="C135" t="n">
         <v>32.75</v>
@@ -3872,7 +3884,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>26.25537490844727</v>
+        <v>26.25537300109863</v>
       </c>
       <c r="C137" t="n">
         <v>33.38999938964844</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>28.00082778930664</v>
+        <v>28.00083541870117</v>
       </c>
       <c r="C138" t="n">
         <v>35.36000061035156</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>27.74148941040039</v>
+        <v>27.74148368835449</v>
       </c>
       <c r="C139" t="n">
         <v>35.03250122070312</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>28.92138671875</v>
+        <v>28.92139625549316</v>
       </c>
       <c r="C140" t="n">
         <v>36.52249908447266</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>29.99186897277832</v>
+        <v>29.99186515808105</v>
       </c>
       <c r="C141" t="n">
         <v>37.62749862670898</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>29.2027645111084</v>
+        <v>29.20276069641113</v>
       </c>
       <c r="C142" t="n">
         <v>36.63750076293945</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>30.90052795410156</v>
+        <v>30.90052604675293</v>
       </c>
       <c r="C143" t="n">
         <v>38.76750183105469</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>31.69179153442383</v>
+        <v>31.69178771972656</v>
       </c>
       <c r="C144" t="n">
         <v>39.5099983215332</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>31.3207950592041</v>
+        <v>31.32080459594727</v>
       </c>
       <c r="C145" t="n">
         <v>39.04750061035156</v>
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>31.76798057556152</v>
+        <v>31.76798820495605</v>
       </c>
       <c r="C146" t="n">
         <v>39.60499954223633</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>30.72894668579102</v>
+        <v>30.72894477844238</v>
       </c>
       <c r="C147" t="n">
         <v>38.03749847412109</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>32.98691940307617</v>
+        <v>32.98690795898438</v>
       </c>
       <c r="C148" t="n">
         <v>40.83250045776367</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>33.10404968261719</v>
+        <v>33.10405731201172</v>
       </c>
       <c r="C149" t="n">
         <v>40.97750091552734</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>33.48779296875</v>
+        <v>33.48778533935547</v>
       </c>
       <c r="C150" t="n">
         <v>41.45249938964844</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>33.96536254882812</v>
+        <v>33.96537399291992</v>
       </c>
       <c r="C151" t="n">
         <v>41.75749969482422</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>34.0690803527832</v>
+        <v>34.06907272338867</v>
       </c>
       <c r="C152" t="n">
         <v>41.8849983215332</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>34.81623840332031</v>
+        <v>34.81623077392578</v>
       </c>
       <c r="C153" t="n">
         <v>42.52500152587891</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>34.30453491210938</v>
+        <v>34.30453109741211</v>
       </c>
       <c r="C154" t="n">
         <v>41.90000152587891</v>
@@ -4423,7 +4435,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>37.42590713500977</v>
+        <v>37.42589569091797</v>
       </c>
       <c r="C156" t="n">
         <v>45.4275016784668</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>35.80083847045898</v>
+        <v>35.80084228515625</v>
       </c>
       <c r="C157" t="n">
         <v>43.45500183105469</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>36.86361312866211</v>
+        <v>36.86360549926758</v>
       </c>
       <c r="C158" t="n">
         <v>44.74499893188477</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>38.92221832275391</v>
+        <v>38.92223358154297</v>
       </c>
       <c r="C159" t="n">
         <v>46.93000030517578</v>
@@ -4568,7 +4580,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>40.3155632019043</v>
+        <v>40.31555557250977</v>
       </c>
       <c r="C161" t="n">
         <v>48.61000061035156</v>
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>41.35709381103516</v>
+        <v>41.35710525512695</v>
       </c>
       <c r="C162" t="n">
         <v>49.5525016784668</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>42.74463653564453</v>
+        <v>42.74465560913086</v>
       </c>
       <c r="C163" t="n">
         <v>51.21500015258789</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>43.22663116455078</v>
+        <v>43.22662734985352</v>
       </c>
       <c r="C164" t="n">
         <v>51.79249954223633</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>45.96819305419922</v>
+        <v>45.96820449829102</v>
       </c>
       <c r="C165" t="n">
         <v>54.77000045776367</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>48.8868522644043</v>
+        <v>48.88684463500977</v>
       </c>
       <c r="C166" t="n">
         <v>58.24750137329102</v>
@@ -4771,7 +4783,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>49.32344436645508</v>
+        <v>49.32344818115234</v>
       </c>
       <c r="C168" t="n">
         <v>58.45500183105469</v>
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>51.08273315429688</v>
+        <v>51.08274078369141</v>
       </c>
       <c r="C169" t="n">
         <v>60.54000091552734</v>
@@ -4858,7 +4870,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>53.59722518920898</v>
+        <v>53.59722900390625</v>
       </c>
       <c r="C171" t="n">
         <v>63.18999862670898</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>51.02296829223633</v>
+        <v>51.02296447753906</v>
       </c>
       <c r="C172" t="n">
         <v>60.15499877929688</v>
@@ -4945,7 +4957,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>54.19096374511719</v>
+        <v>54.19095611572266</v>
       </c>
       <c r="C174" t="n">
         <v>63.88999938964844</v>
@@ -5003,7 +5015,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>59.8497314453125</v>
+        <v>59.84971237182617</v>
       </c>
       <c r="C176" t="n">
         <v>70.17500305175781</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>59.82367706298828</v>
+        <v>59.82367324829102</v>
       </c>
       <c r="C177" t="n">
         <v>69.79250335693359</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>59.47867584228516</v>
+        <v>59.47865676879883</v>
       </c>
       <c r="C178" t="n">
         <v>69.38999938964844</v>
@@ -5119,7 +5131,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5148,11 +5160,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>63.37459564208984</v>
+        <v>63.37459945678711</v>
       </c>
       <c r="C180" t="n">
         <v>73.58999633789062</v>
@@ -5177,11 +5189,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>66.44040679931641</v>
+        <v>66.44041442871094</v>
       </c>
       <c r="C181" t="n">
         <v>77.15000152587891</v>
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>69.64402770996094</v>
+        <v>69.64402008056641</v>
       </c>
       <c r="C182" t="n">
         <v>80.87000274658203</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>63.61191558837891</v>
+        <v>63.61189651489258</v>
       </c>
       <c r="C183" t="n">
         <v>73.48000335693359</v>
@@ -5264,11 +5276,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>65.45584869384766</v>
+        <v>65.45584106445312</v>
       </c>
       <c r="C184" t="n">
         <v>75.61000061035156</v>
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>67.10067749023438</v>
+        <v>67.10066986083984</v>
       </c>
       <c r="C185" t="n">
         <v>77.51000213623047</v>
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>63.38682556152344</v>
+        <v>63.38681793212891</v>
       </c>
       <c r="C186" t="n">
         <v>73.22000122070312</v>
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>63.77407455444336</v>
+        <v>63.77408981323242</v>
       </c>
       <c r="C187" t="n">
         <v>73.27999877929688</v>
@@ -5380,11 +5392,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>67.79478454589844</v>
+        <v>67.79477691650391</v>
       </c>
       <c r="C188" t="n">
         <v>77.90000152587891</v>
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>73.42923736572266</v>
+        <v>73.42922210693359</v>
       </c>
       <c r="C189" t="n">
         <v>83.98999786376953</v>
@@ -5438,7 +5450,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5467,7 +5479,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>76.20442962646484</v>
+        <v>76.20443725585938</v>
       </c>
       <c r="C192" t="n">
         <v>86.77999877929688</v>
@@ -5525,11 +5537,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>81.98255920410156</v>
+        <v>81.98257446289062</v>
       </c>
       <c r="C193" t="n">
         <v>93.36000061035156</v>
@@ -5554,7 +5566,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>69.1121826171875</v>
+        <v>69.11219024658203</v>
       </c>
       <c r="C195" t="n">
         <v>78.26999664306641</v>
@@ -5612,11 +5624,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>74.79868316650391</v>
+        <v>74.79869079589844</v>
       </c>
       <c r="C196" t="n">
         <v>84.70999908447266</v>
@@ -5641,7 +5653,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5670,11 +5682,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>67.21474456787109</v>
+        <v>67.21475219726562</v>
       </c>
       <c r="C198" t="n">
         <v>75.69000244140625</v>
@@ -5699,11 +5711,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>68.78655242919922</v>
+        <v>68.78653717041016</v>
       </c>
       <c r="C199" t="n">
         <v>77.45999908447266</v>
@@ -5728,11 +5740,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>75.02938079833984</v>
+        <v>75.02937316894531</v>
       </c>
       <c r="C200" t="n">
         <v>84.48999786376953</v>
@@ -5757,11 +5769,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>75.90187835693359</v>
+        <v>75.90186309814453</v>
       </c>
       <c r="C201" t="n">
         <v>85.05999755859375</v>
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>69.96786499023438</v>
+        <v>69.96784973144531</v>
       </c>
       <c r="C202" t="n">
         <v>78.41000366210938</v>
@@ -5815,11 +5827,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>69.15583038330078</v>
+        <v>69.15581512451172</v>
       </c>
       <c r="C203" t="n">
         <v>77.5</v>
@@ -5844,11 +5856,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>75.96445465087891</v>
+        <v>75.9644775390625</v>
       </c>
       <c r="C204" t="n">
         <v>84.69999694824219</v>
@@ -5873,11 +5885,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>74.97792053222656</v>
+        <v>74.97791290283203</v>
       </c>
       <c r="C205" t="n">
         <v>83.59999847412109</v>
@@ -5902,11 +5914,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>66.93302917480469</v>
+        <v>66.93302154541016</v>
       </c>
       <c r="C206" t="n">
         <v>74.62999725341797</v>
@@ -5931,7 +5943,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5960,7 +5972,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5989,11 +6001,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>69.17070770263672</v>
+        <v>69.17070007324219</v>
       </c>
       <c r="C209" t="n">
         <v>76.62999725341797</v>
@@ -6018,7 +6030,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6047,11 +6059,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>67.40708923339844</v>
+        <v>67.40709686279297</v>
       </c>
       <c r="C211" t="n">
         <v>74.19999694824219</v>
@@ -6076,11 +6088,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>66.58949279785156</v>
+        <v>66.58948516845703</v>
       </c>
       <c r="C212" t="n">
         <v>73.30000305175781</v>
@@ -6105,11 +6117,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>61.10498046875</v>
+        <v>61.1049690246582</v>
       </c>
       <c r="C213" t="n">
         <v>66.80000305175781</v>
@@ -6134,11 +6146,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>52.40574645996094</v>
+        <v>52.4057502746582</v>
       </c>
       <c r="C214" t="n">
         <v>57.29000091552734</v>
@@ -6163,11 +6175,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>53.32964324951172</v>
+        <v>53.32964706420898</v>
       </c>
       <c r="C215" t="n">
         <v>58.29999923706055</v>
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>53.9572639465332</v>
+        <v>53.95726776123047</v>
       </c>
       <c r="C216" t="n">
         <v>58.5099983215332</v>
@@ -6221,11 +6233,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>56.01374816894531</v>
+        <v>56.01374053955078</v>
       </c>
       <c r="C217" t="n">
         <v>60.7400016784668</v>
@@ -6250,11 +6262,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>54.06792449951172</v>
+        <v>54.06793212890625</v>
       </c>
       <c r="C218" t="n">
         <v>58.63000106811523</v>
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>51.36145401000977</v>
+        <v>51.3614501953125</v>
       </c>
       <c r="C219" t="n">
         <v>55.18999862670898</v>
@@ -6308,11 +6320,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>59.47654342651367</v>
+        <v>59.47654724121094</v>
       </c>
       <c r="C220" t="n">
         <v>63.90999984741211</v>
@@ -6337,11 +6349,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>62.32426834106445</v>
+        <v>62.32428359985352</v>
       </c>
       <c r="C221" t="n">
         <v>66.97000122070312</v>
@@ -6366,7 +6378,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6395,11 +6407,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>66.32474517822266</v>
+        <v>66.32473754882812</v>
       </c>
       <c r="C223" t="n">
         <v>70.80999755859375</v>
@@ -6424,11 +6436,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>71.55129241943359</v>
+        <v>71.55130004882812</v>
       </c>
       <c r="C224" t="n">
         <v>76.38999938964844</v>
@@ -6453,11 +6465,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>75.89875030517578</v>
+        <v>75.89875793457031</v>
       </c>
       <c r="C225" t="n">
         <v>80.51000213623047</v>
@@ -6482,7 +6494,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6511,7 +6523,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6540,7 +6552,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6569,11 +6581,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>68.03684997558594</v>
+        <v>68.03685760498047</v>
       </c>
       <c r="C229" t="n">
         <v>71.69000244140625</v>
@@ -6598,11 +6610,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>67.91345977783203</v>
+        <v>67.91346740722656</v>
       </c>
       <c r="C230" t="n">
         <v>71.55999755859375</v>
@@ -6627,7 +6639,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6656,11 +6668,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>67.83196258544922</v>
+        <v>67.83195495605469</v>
       </c>
       <c r="C232" t="n">
         <v>70.88999938964844</v>
@@ -6685,7 +6697,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6714,7 +6726,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6743,11 +6755,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>66.96286010742188</v>
+        <v>66.96285247802734</v>
       </c>
       <c r="C235" t="n">
         <v>69.41999816894531</v>
@@ -6772,11 +6784,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>68.54480743408203</v>
+        <v>68.54481506347656</v>
       </c>
       <c r="C236" t="n">
         <v>71.05999755859375</v>
@@ -6801,7 +6813,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6830,7 +6842,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6888,7 +6900,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6917,7 +6929,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>77.01999664306641</v>
+        <v>75.62000274658203</v>
       </c>
       <c r="C250" t="n">
-        <v>77.01999664306641</v>
+        <v>75.62000274658203</v>
       </c>
       <c r="D250" t="n">
-        <v>180429200</v>
+        <v>195530500</v>
       </c>
       <c r="E250" t="n">
         <v>4.46</v>
       </c>
       <c r="F250" t="n">
-        <v>17.26905754328843</v>
+        <v>16.95515756649821</v>
       </c>
       <c r="G250" t="n">
         <v>2085341456</v>
       </c>
       <c r="H250" t="n">
-        <v>160612991940.7672</v>
+        <v>157693526630.2814</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08652261694643067</v>
+        <v>0.09376426073409438</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I7" t="n">
         <v>0.9925</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K7" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I8" t="n">
         <v>1.1075</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K8" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I9" t="n">
         <v>1.1325</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K9" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I10" t="n">
         <v>1.24</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I11" t="n">
         <v>1.185</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K11" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I12" t="n">
         <v>1.005</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="K12" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I13" t="n">
         <v>1.0975</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="K13" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I14" t="n">
         <v>0.905</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K14" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I15" t="n">
         <v>1.145</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K15" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I16" t="n">
         <v>1.2625</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="K16" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I17" t="n">
         <v>1.28</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="K17" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I18" t="n">
         <v>1.2825</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="K18" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I19" t="n">
         <v>1.14</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K19" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I20" t="n">
         <v>1.0225</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K20" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I21" t="n">
         <v>1.02</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="K21" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I22" t="n">
         <v>1.185</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K22" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I23" t="n">
         <v>1.1175</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="K23" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I24" t="n">
         <v>1.2025</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K24" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I25" t="n">
         <v>1.1225</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K25" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I26" t="n">
         <v>1.0875</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="K26" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I27" t="n">
         <v>1.4</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K27" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I28" t="n">
         <v>1.5175</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="K28" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I29" t="n">
         <v>1.635</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="K29" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I30" t="n">
         <v>1.7425</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K30" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42422</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I31" t="n">
         <v>1.5175</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42422</v>
       </c>
       <c r="K31" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I32" t="n">
         <v>1.4975</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K32" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I33" t="n">
         <v>1.39</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K33" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I34" t="n">
         <v>1.3125</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K34" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I35" t="n">
         <v>1.5525</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K35" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I36" t="n">
         <v>2.0525</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="K36" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I37" t="n">
         <v>2.1825</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="K37" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I38" t="n">
         <v>2.225</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K38" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I39" t="n">
         <v>2.8475</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="K39" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I40" t="n">
         <v>4.335</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="K40" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I41" t="n">
         <v>4.325</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K41" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I42" t="n">
         <v>4.4025</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="K42" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I43" t="n">
         <v>3.485</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="K43" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I44" t="n">
         <v>1.5075</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="K44" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I45" t="n">
         <v>1.7375</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="K45" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I46" t="n">
         <v>1.665</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="K46" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I47" t="n">
         <v>1.9425</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="K47" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I48" t="n">
         <v>1.805</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="K48" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I49" t="n">
         <v>1.8125</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="K49" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I50" t="n">
         <v>1.985</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="K50" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I51" t="n">
         <v>1.4875</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="K51" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I52" t="n">
         <v>2.1125</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="K52" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44403</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I53" t="n">
         <v>1.595</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44403</v>
       </c>
       <c r="K53" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44494</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I54" t="n">
         <v>1.2</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44494</v>
       </c>
       <c r="K54" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I55" t="n">
         <v>1.81</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="K55" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I56" t="n">
         <v>0.7400000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="K56" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I57" t="n">
         <v>1.31</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K57" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I58" t="n">
         <v>1.94</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K58" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I59" t="n">
         <v>2.1</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="K59" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I60" t="n">
         <v>3.37</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K60" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I61" t="n">
         <v>4.05</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="K61" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I62" t="n">
         <v>3.79</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="K62" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I63" t="n">
         <v>3.6</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="K63" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I64" t="n">
         <v>3.66</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="K64" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I65" t="n">
         <v>3.07</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="K65" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I66" t="n">
         <v>3.37</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="K66" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I67" t="n">
         <v>3.37</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="K67" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I68" t="n">
         <v>2.67</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K68" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I69" t="n">
         <v>2.86</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="K69" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I70" t="n">
         <v>3.14</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="K70" t="n">
@@ -10451,13 +10463,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10484,7 +10496,7 @@
       <c r="I71" t="n">
         <v>3.3</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="K71" t="n">
@@ -10497,13 +10509,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10530,7 +10542,7 @@
       <c r="I72" t="n">
         <v>3.94</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="K72" t="n">
@@ -10543,13 +10555,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10570,7 +10582,7 @@
       <c r="I73" t="n">
         <v>4.46</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K73" t="n">
@@ -10607,52 +10619,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="C2" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="C3" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40301</v>
       </c>
       <c r="C5" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C6" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C7" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="C8" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="C9" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C10" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C11" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="C12" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="C13" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="C14" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C15" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C16" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="C17" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C18" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41694</v>
       </c>
       <c r="C19" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C20" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C21" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41950</v>
       </c>
       <c r="C22" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C23" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C24" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="C25" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C26" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42422</v>
       </c>
       <c r="C27" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C28" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C29" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C30" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C31" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="C32" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="C33" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C34" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="C35" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43214</v>
       </c>
       <c r="C36" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C37" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43396</v>
       </c>
       <c r="C38" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="C39" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43578</v>
       </c>
       <c r="C40" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43670</v>
       </c>
       <c r="C41" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="C42" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="C43" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="C44" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="C45" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="C46" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="C47" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="C48" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44403</v>
       </c>
       <c r="C49" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44494</v>
       </c>
       <c r="C50" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="C51" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="C52" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C53" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C54" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="C55" t="n">
@@ -12377,10 +12389,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C56" t="n">
@@ -12409,10 +12421,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="C57" t="n">
@@ -12441,10 +12453,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45237</v>
       </c>
       <c r="C58" t="n">
@@ -12473,10 +12485,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="C59" t="n">
@@ -12505,10 +12517,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="C60" t="n">
@@ -12537,10 +12549,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="C61" t="n">
@@ -12569,10 +12581,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45588</v>
       </c>
       <c r="C62" t="n">
@@ -12601,10 +12613,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="C63" t="n">
@@ -12633,10 +12645,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="C64" t="n">
@@ -12665,10 +12677,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="C65" t="n">
@@ -12697,10 +12709,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="C66" t="n">
@@ -12729,10 +12741,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C67" t="n">
@@ -12761,10 +12773,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="C68" t="n">
@@ -12811,12 +12823,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/NEE.xlsx
+++ b/salidas/empresas/NEE.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>5.649925708770752</v>
+        <v>5.649928092956543</v>
       </c>
       <c r="C2" t="n">
         <v>10.44750022888184</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>5.6688551902771</v>
+        <v>5.668856143951416</v>
       </c>
       <c r="C3" t="n">
         <v>10.48250007629395</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>5.476528167724609</v>
+        <v>5.476527690887451</v>
       </c>
       <c r="C4" t="n">
         <v>10.03499984741211</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>5.402852058410645</v>
+        <v>5.402850151062012</v>
       </c>
       <c r="C5" t="n">
         <v>9.899999618530273</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>5.434232711791992</v>
+        <v>5.434232234954834</v>
       </c>
       <c r="C6" t="n">
         <v>9.957500457763672</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>5.697667121887207</v>
+        <v>5.697669506072998</v>
       </c>
       <c r="C7" t="n">
         <v>10.34500026702881</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>5.940006256103516</v>
+        <v>5.940004825592041</v>
       </c>
       <c r="C8" t="n">
         <v>10.78499984741211</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>6.172992706298828</v>
+        <v>6.172990798950195</v>
       </c>
       <c r="C9" t="n">
         <v>11.11250019073486</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>6.249371528625488</v>
+        <v>6.249373912811279</v>
       </c>
       <c r="C10" t="n">
         <v>11.25</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>7.082620620727539</v>
+        <v>7.082622051239014</v>
       </c>
       <c r="C11" t="n">
         <v>12.75</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>7.611706733703613</v>
+        <v>7.611709594726562</v>
       </c>
       <c r="C13" t="n">
         <v>13.60499954223633</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>7.923617839813232</v>
+        <v>7.923619747161865</v>
       </c>
       <c r="C14" t="n">
         <v>14.16250038146973</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>8.615445137023926</v>
+        <v>8.615447044372559</v>
       </c>
       <c r="C16" t="n">
         <v>15.29249954223633</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>9.066149711608887</v>
+        <v>9.066147804260254</v>
       </c>
       <c r="C17" t="n">
         <v>16.09250068664551</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>9.004178047180176</v>
+        <v>9.004177093505859</v>
       </c>
       <c r="C18" t="n">
         <v>15.98250007629395</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>8.045281410217285</v>
+        <v>8.045282363891602</v>
       </c>
       <c r="C19" t="n">
         <v>14.1850004196167</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>8.18565559387207</v>
+        <v>8.185654640197754</v>
       </c>
       <c r="C20" t="n">
         <v>14.43249988555908</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>8.40321159362793</v>
+        <v>8.403215408325195</v>
       </c>
       <c r="C21" t="n">
         <v>14.71000003814697</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>8.694559097290039</v>
+        <v>8.69455623626709</v>
       </c>
       <c r="C22" t="n">
         <v>15.22000026702881</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>9.771376609802246</v>
+        <v>9.771374702453613</v>
       </c>
       <c r="C23" t="n">
         <v>17.10499954223633</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>10.02323627471924</v>
+        <v>10.02323818206787</v>
       </c>
       <c r="C24" t="n">
         <v>17.44000053405762</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>9.738747596740723</v>
+        <v>9.738743782043457</v>
       </c>
       <c r="C25" t="n">
         <v>16.94499969482422</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>9.245919227600098</v>
+        <v>9.245918273925781</v>
       </c>
       <c r="C26" t="n">
         <v>16.08749961853027</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>9.076876640319824</v>
+        <v>9.076875686645508</v>
       </c>
       <c r="C28" t="n">
         <v>15.6850004196167</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>9.768418312072754</v>
+        <v>9.768420219421387</v>
       </c>
       <c r="C30" t="n">
         <v>16.8799991607666</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>9.55234432220459</v>
+        <v>9.552345275878906</v>
       </c>
       <c r="C31" t="n">
         <v>16.39500045776367</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>9.399404525756836</v>
+        <v>9.399397850036621</v>
       </c>
       <c r="C32" t="n">
         <v>16.13249969482422</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>8.812769889831543</v>
+        <v>8.812771797180176</v>
       </c>
       <c r="C33" t="n">
         <v>15.01500034332275</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>7.380659580230713</v>
+        <v>7.380660533905029</v>
       </c>
       <c r="C34" t="n">
         <v>12.57499980926514</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>6.931660175323486</v>
+        <v>6.931659698486328</v>
       </c>
       <c r="C35" t="n">
         <v>11.8100004196167</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>7.221139430999756</v>
+        <v>7.22114086151123</v>
       </c>
       <c r="C36" t="n">
         <v>12.1899995803833</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>7.453651905059814</v>
+        <v>7.453649997711182</v>
       </c>
       <c r="C37" t="n">
         <v>12.58250045776367</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>7.634324550628662</v>
+        <v>7.634328365325928</v>
       </c>
       <c r="C38" t="n">
         <v>12.88749980926514</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>7.585970878601074</v>
+        <v>7.585968494415283</v>
       </c>
       <c r="C40" t="n">
         <v>12.68249988555908</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>8.043550491333008</v>
+        <v>8.043547630310059</v>
       </c>
       <c r="C41" t="n">
         <v>13.44750022888184</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>8.453275680541992</v>
+        <v>8.453276634216309</v>
       </c>
       <c r="C42" t="n">
         <v>14.13249969482422</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>8.572911262512207</v>
+        <v>8.572915077209473</v>
       </c>
       <c r="C43" t="n">
         <v>14.21500015258789</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>8.544266700744629</v>
+        <v>8.544265747070312</v>
       </c>
       <c r="C44" t="n">
         <v>14.16749954223633</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>8.540253639221191</v>
+        <v>8.540251731872559</v>
       </c>
       <c r="C45" t="n">
         <v>14.04500007629395</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>8.395835876464844</v>
+        <v>8.395837783813477</v>
       </c>
       <c r="C46" t="n">
         <v>13.80749988555908</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>7.463978290557861</v>
+        <v>7.463977813720703</v>
       </c>
       <c r="C47" t="n">
         <v>12.27499961853027</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>7.972771167755127</v>
+        <v>7.972772598266602</v>
       </c>
       <c r="C48" t="n">
         <v>12.99250030517578</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>8.10317325592041</v>
+        <v>8.103174209594727</v>
       </c>
       <c r="C49" t="n">
         <v>13.20499992370605</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>7.480321884155273</v>
+        <v>7.480325222015381</v>
       </c>
       <c r="C50" t="n">
         <v>12.1899995803833</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>7.190491676330566</v>
+        <v>7.190493106842041</v>
       </c>
       <c r="C51" t="n">
         <v>11.59249973297119</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>7.494425773620605</v>
+        <v>7.49442720413208</v>
       </c>
       <c r="C52" t="n">
         <v>12.08250045776367</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>8.07127571105957</v>
+        <v>8.07127857208252</v>
       </c>
       <c r="C53" t="n">
         <v>13.01249980926514</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.742534160614014</v>
+        <v>7.74253511428833</v>
       </c>
       <c r="C54" t="n">
         <v>12.48250007629395</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>7.639151573181152</v>
+        <v>7.639147758483887</v>
       </c>
       <c r="C55" t="n">
         <v>12.1899995803833</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>8.193757057189941</v>
+        <v>8.193756103515625</v>
       </c>
       <c r="C56" t="n">
         <v>13.07499980926514</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>8.496038436889648</v>
+        <v>8.496040344238281</v>
       </c>
       <c r="C57" t="n">
         <v>13.43249988555908</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>8.703182220458984</v>
+        <v>8.703181266784668</v>
       </c>
       <c r="C59" t="n">
         <v>13.76000022888184</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>8.300576210021973</v>
+        <v>8.300578117370605</v>
       </c>
       <c r="C61" t="n">
         <v>12.9975004196167</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>8.535271644592285</v>
+        <v>8.535273551940918</v>
       </c>
       <c r="C62" t="n">
         <v>13.36499977111816</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>8.856184959411621</v>
+        <v>8.856184005737305</v>
       </c>
       <c r="C63" t="n">
         <v>13.86750030517578</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>9.347110748291016</v>
+        <v>9.347109794616699</v>
       </c>
       <c r="C66" t="n">
         <v>14.48750019073486</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>9.356881141662598</v>
+        <v>9.356879234313965</v>
       </c>
       <c r="C67" t="n">
         <v>14.36499977111816</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>8.996999740600586</v>
+        <v>8.996997833251953</v>
       </c>
       <c r="C68" t="n">
         <v>13.8125</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>9.329469680786133</v>
+        <v>9.3294677734375</v>
       </c>
       <c r="C69" t="n">
         <v>14.18000030517578</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>9.276830673217773</v>
+        <v>9.276834487915039</v>
       </c>
       <c r="C71" t="n">
         <v>14.10000038146973</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>9.211551666259766</v>
+        <v>9.211548805236816</v>
       </c>
       <c r="C72" t="n">
         <v>13.85999965667725</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>10.11542701721191</v>
+        <v>10.11542797088623</v>
       </c>
       <c r="C73" t="n">
         <v>15.22000026702881</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>9.986867904663086</v>
+        <v>9.986869812011719</v>
       </c>
       <c r="C75" t="n">
         <v>14.8774995803833</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>10.25034713745117</v>
+        <v>10.2503490447998</v>
       </c>
       <c r="C76" t="n">
         <v>15.27000045776367</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>11.06714725494385</v>
+        <v>11.06714153289795</v>
       </c>
       <c r="C78" t="n">
         <v>16.33499908447266</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>12.00888061523438</v>
+        <v>12.00888347625732</v>
       </c>
       <c r="C80" t="n">
         <v>17.72500038146973</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>11.50172710418701</v>
+        <v>11.50172519683838</v>
       </c>
       <c r="C81" t="n">
         <v>16.82749938964844</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>12.0177755355835</v>
+        <v>12.01777267456055</v>
       </c>
       <c r="C82" t="n">
         <v>17.58250045776367</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>11.97163200378418</v>
+        <v>11.97163772583008</v>
       </c>
       <c r="C83" t="n">
         <v>17.51499938964844</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>11.84575462341309</v>
+        <v>11.84575366973877</v>
       </c>
       <c r="C84" t="n">
         <v>17.17749977111816</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>11.92850589752197</v>
+        <v>11.92850685119629</v>
       </c>
       <c r="C85" t="n">
         <v>17.29750061035156</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>12.42157363891602</v>
+        <v>12.42158126831055</v>
       </c>
       <c r="C86" t="n">
         <v>18.01250076293945</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>12.50474262237549</v>
+        <v>12.50474548339844</v>
       </c>
       <c r="C87" t="n">
         <v>17.96750068664551</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>13.51562786102295</v>
+        <v>13.51562976837158</v>
       </c>
       <c r="C88" t="n">
         <v>19.42000007629395</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>14.27248954772949</v>
+        <v>14.27249622344971</v>
       </c>
       <c r="C89" t="n">
         <v>20.50749969482422</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>15.20187568664551</v>
+        <v>15.20187759399414</v>
       </c>
       <c r="C92" t="n">
         <v>21.65250015258789</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>14.22061061859131</v>
+        <v>14.22061347961426</v>
       </c>
       <c r="C93" t="n">
         <v>20.09000015258789</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>14.18521881103516</v>
+        <v>14.18522071838379</v>
       </c>
       <c r="C94" t="n">
         <v>20.04000091552734</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>14.99747753143311</v>
+        <v>14.99747467041016</v>
       </c>
       <c r="C95" t="n">
         <v>21.1875</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>15.08479404449463</v>
+        <v>15.08479022979736</v>
       </c>
       <c r="C96" t="n">
         <v>21.14749908447266</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>15.26846790313721</v>
+        <v>15.26847267150879</v>
       </c>
       <c r="C97" t="n">
         <v>21.40500068664551</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>16.42738723754883</v>
+        <v>16.4273853302002</v>
       </c>
       <c r="C99" t="n">
         <v>22.84749984741211</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>17.18773651123047</v>
+        <v>17.1877326965332</v>
       </c>
       <c r="C100" t="n">
         <v>23.90500068664551</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>17.94807434082031</v>
+        <v>17.94807624816895</v>
       </c>
       <c r="C101" t="n">
         <v>24.96249961853027</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>17.63179206848145</v>
+        <v>17.63179779052734</v>
       </c>
       <c r="C102" t="n">
         <v>24.34000015258789</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>18.55901908874512</v>
+        <v>18.55902481079102</v>
       </c>
       <c r="C103" t="n">
         <v>25.6200008392334</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>17.00337982177734</v>
+        <v>17.00338363647461</v>
       </c>
       <c r="C104" t="n">
         <v>23.47249984741211</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>17.96384811401367</v>
+        <v>17.96384620666504</v>
       </c>
       <c r="C105" t="n">
         <v>24.61249923706055</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>18.28680992126465</v>
+        <v>18.28681755065918</v>
       </c>
       <c r="C107" t="n">
         <v>25.05500030517578</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>19.53157424926758</v>
+        <v>19.53157615661621</v>
       </c>
       <c r="C109" t="n">
         <v>26.57250022888184</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>20.07365036010742</v>
+        <v>20.07366180419922</v>
       </c>
       <c r="C110" t="n">
         <v>27.30999946594238</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>19.15054321289062</v>
+        <v>19.15054512023926</v>
       </c>
       <c r="C111" t="n">
         <v>25.86499977111816</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>19.25976181030273</v>
+        <v>19.25975227355957</v>
       </c>
       <c r="C112" t="n">
         <v>26.01250076293945</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>18.68223762512207</v>
+        <v>18.68223571777344</v>
       </c>
       <c r="C113" t="n">
         <v>25.23250007629395</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>19.08871269226074</v>
+        <v>19.08871841430664</v>
       </c>
       <c r="C114" t="n">
         <v>25.58499908447266</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>18.28480911254883</v>
+        <v>18.28480339050293</v>
       </c>
       <c r="C115" t="n">
         <v>24.50749969482422</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>19.62217140197754</v>
+        <v>19.62217330932617</v>
       </c>
       <c r="C116" t="n">
         <v>26.29999923706055</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>18.49739456176758</v>
+        <v>18.49739265441895</v>
       </c>
       <c r="C117" t="n">
         <v>24.60250091552734</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>18.33574867248535</v>
+        <v>18.33574676513672</v>
       </c>
       <c r="C118" t="n">
         <v>24.38750076293945</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>19.29623985290527</v>
+        <v>19.29622840881348</v>
       </c>
       <c r="C119" t="n">
         <v>25.66500091552734</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>18.91487121582031</v>
+        <v>18.91486930847168</v>
       </c>
       <c r="C120" t="n">
         <v>24.96500015258789</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>21.15942573547363</v>
+        <v>21.1594295501709</v>
       </c>
       <c r="C122" t="n">
         <v>27.92749977111816</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>22.58444786071777</v>
+        <v>22.58444404602051</v>
       </c>
       <c r="C124" t="n">
         <v>29.58499908447266</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>22.43940925598145</v>
+        <v>22.43940734863281</v>
       </c>
       <c r="C125" t="n">
         <v>29.39500045776367</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>25.06915664672852</v>
+        <v>25.06914710998535</v>
       </c>
       <c r="C127" t="n">
         <v>32.59999847412109</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>24.66350555419922</v>
+        <v>24.66350936889648</v>
       </c>
       <c r="C128" t="n">
         <v>32.0724983215332</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>23.41409111022949</v>
+        <v>23.41409492492676</v>
       </c>
       <c r="C129" t="n">
         <v>30.23500061035156</v>
@@ -3714,7 +3714,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>23.68125343322754</v>
+        <v>23.6812572479248</v>
       </c>
       <c r="C130" t="n">
         <v>30.57999992370605</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>24.78091239929199</v>
+        <v>24.78090667724609</v>
       </c>
       <c r="C131" t="n">
         <v>32</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>22.28456878662109</v>
+        <v>22.28457641601562</v>
       </c>
       <c r="C132" t="n">
         <v>28.5575008392334</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>24.13592910766602</v>
+        <v>24.13592338562012</v>
       </c>
       <c r="C134" t="n">
         <v>30.93000030517578</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>25.75212669372559</v>
+        <v>25.75213241577148</v>
       </c>
       <c r="C135" t="n">
         <v>32.75</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>25.23511695861816</v>
+        <v>25.23511505126953</v>
       </c>
       <c r="C136" t="n">
         <v>32.09249877929688</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>26.25537300109863</v>
+        <v>26.25536727905273</v>
       </c>
       <c r="C137" t="n">
         <v>33.38999938964844</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>28.00083541870117</v>
+        <v>28.00083160400391</v>
       </c>
       <c r="C138" t="n">
         <v>35.36000061035156</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>28.92139625549316</v>
+        <v>28.92138671875</v>
       </c>
       <c r="C140" t="n">
         <v>36.52249908447266</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>29.99186515808105</v>
+        <v>29.99186325073242</v>
       </c>
       <c r="C141" t="n">
         <v>37.62749862670898</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>30.90052604675293</v>
+        <v>30.9005298614502</v>
       </c>
       <c r="C143" t="n">
         <v>38.76750183105469</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>31.69178771972656</v>
+        <v>31.69178009033203</v>
       </c>
       <c r="C144" t="n">
         <v>39.5099983215332</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>31.32080459594727</v>
+        <v>31.32080078125</v>
       </c>
       <c r="C145" t="n">
         <v>39.04750061035156</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>31.76798820495605</v>
+        <v>31.76799583435059</v>
       </c>
       <c r="C146" t="n">
         <v>39.60499954223633</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>30.72894477844238</v>
+        <v>30.72895050048828</v>
       </c>
       <c r="C147" t="n">
         <v>38.03749847412109</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>32.98690795898438</v>
+        <v>32.98691177368164</v>
       </c>
       <c r="C148" t="n">
         <v>40.83250045776367</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>33.10405731201172</v>
+        <v>33.10405349731445</v>
       </c>
       <c r="C149" t="n">
         <v>40.97750091552734</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>33.96537399291992</v>
+        <v>33.96537017822266</v>
       </c>
       <c r="C151" t="n">
         <v>41.75749969482422</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>34.06907272338867</v>
+        <v>34.0690803527832</v>
       </c>
       <c r="C152" t="n">
         <v>41.8849983215332</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>34.81623077392578</v>
+        <v>34.81623840332031</v>
       </c>
       <c r="C153" t="n">
         <v>42.52500152587891</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>34.30453109741211</v>
+        <v>34.30452728271484</v>
       </c>
       <c r="C154" t="n">
         <v>41.90000152587891</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>35.30746841430664</v>
+        <v>35.30747222900391</v>
       </c>
       <c r="C155" t="n">
         <v>43.125</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>37.42589569091797</v>
+        <v>37.42589950561523</v>
       </c>
       <c r="C156" t="n">
         <v>45.4275016784668</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>35.80084228515625</v>
+        <v>35.80083465576172</v>
       </c>
       <c r="C157" t="n">
         <v>43.45500183105469</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>38.92223358154297</v>
+        <v>38.9222412109375</v>
       </c>
       <c r="C159" t="n">
         <v>46.93000030517578</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>40.08333206176758</v>
+        <v>40.08334350585938</v>
       </c>
       <c r="C160" t="n">
         <v>48.33000183105469</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>40.31555557250977</v>
+        <v>40.3155632019043</v>
       </c>
       <c r="C161" t="n">
         <v>48.61000061035156</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>41.35710525512695</v>
+        <v>41.35710144042969</v>
       </c>
       <c r="C162" t="n">
         <v>49.5525016784668</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>42.74465560913086</v>
+        <v>42.74465179443359</v>
       </c>
       <c r="C163" t="n">
         <v>51.21500015258789</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>45.96820449829102</v>
+        <v>45.96818923950195</v>
       </c>
       <c r="C165" t="n">
         <v>54.77000045776367</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>48.88684463500977</v>
+        <v>48.88684844970703</v>
       </c>
       <c r="C166" t="n">
         <v>58.24750137329102</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>49.32344818115234</v>
+        <v>49.32344055175781</v>
       </c>
       <c r="C168" t="n">
         <v>58.45500183105469</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>51.08274078369141</v>
+        <v>51.08274459838867</v>
       </c>
       <c r="C169" t="n">
         <v>60.54000091552734</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>56.57577896118164</v>
+        <v>56.57578277587891</v>
       </c>
       <c r="C170" t="n">
         <v>67.05000305175781</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>53.59722900390625</v>
+        <v>53.59722518920898</v>
       </c>
       <c r="C171" t="n">
         <v>63.18999862670898</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>51.02296447753906</v>
+        <v>51.0229606628418</v>
       </c>
       <c r="C172" t="n">
         <v>60.15499877929688</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>49.00850677490234</v>
+        <v>49.00851058959961</v>
       </c>
       <c r="C173" t="n">
         <v>57.77999877929688</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>54.19095611572266</v>
+        <v>54.19096755981445</v>
       </c>
       <c r="C174" t="n">
         <v>63.88999938964844</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>59.84971237182617</v>
+        <v>59.84970474243164</v>
       </c>
       <c r="C176" t="n">
         <v>70.17500305175781</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>59.82367324829102</v>
+        <v>59.82367706298828</v>
       </c>
       <c r="C177" t="n">
         <v>69.79250335693359</v>
@@ -5106,7 +5106,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>59.47865676879883</v>
+        <v>59.47869110107422</v>
       </c>
       <c r="C178" t="n">
         <v>69.38999938964844</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>63.37459945678711</v>
+        <v>63.37458038330078</v>
       </c>
       <c r="C180" t="n">
         <v>73.58999633789062</v>
@@ -5193,7 +5193,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>66.44041442871094</v>
+        <v>66.44042205810547</v>
       </c>
       <c r="C181" t="n">
         <v>77.15000152587891</v>
@@ -5222,7 +5222,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>69.64402008056641</v>
+        <v>69.64403533935547</v>
       </c>
       <c r="C182" t="n">
         <v>80.87000274658203</v>
@@ -5251,7 +5251,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>63.61189651489258</v>
+        <v>63.61191558837891</v>
       </c>
       <c r="C183" t="n">
         <v>73.48000335693359</v>
@@ -5280,7 +5280,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>65.45584106445312</v>
+        <v>65.45581817626953</v>
       </c>
       <c r="C184" t="n">
         <v>75.61000061035156</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>67.10066986083984</v>
+        <v>67.10068511962891</v>
       </c>
       <c r="C185" t="n">
         <v>77.51000213623047</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>63.77408981323242</v>
+        <v>63.77408599853516</v>
       </c>
       <c r="C187" t="n">
         <v>73.27999877929688</v>
@@ -5396,7 +5396,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>67.79477691650391</v>
+        <v>67.79478454589844</v>
       </c>
       <c r="C188" t="n">
         <v>77.90000152587891</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>68.64701080322266</v>
+        <v>68.64699554443359</v>
       </c>
       <c r="C190" t="n">
         <v>78.51999664306641</v>
@@ -5541,7 +5541,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>81.98257446289062</v>
+        <v>81.98256683349609</v>
       </c>
       <c r="C193" t="n">
         <v>93.36000061035156</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>69.11219024658203</v>
+        <v>69.1121826171875</v>
       </c>
       <c r="C195" t="n">
         <v>78.26999664306641</v>
@@ -5686,7 +5686,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>67.21475219726562</v>
+        <v>67.21473693847656</v>
       </c>
       <c r="C198" t="n">
         <v>75.69000244140625</v>
@@ -5715,7 +5715,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>68.78653717041016</v>
+        <v>68.78654479980469</v>
       </c>
       <c r="C199" t="n">
         <v>77.45999908447266</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>69.15581512451172</v>
+        <v>69.15583038330078</v>
       </c>
       <c r="C203" t="n">
         <v>77.5</v>
@@ -5860,7 +5860,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>75.9644775390625</v>
+        <v>75.96444702148438</v>
       </c>
       <c r="C204" t="n">
         <v>84.69999694824219</v>
@@ -5889,7 +5889,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>74.97791290283203</v>
+        <v>74.97792053222656</v>
       </c>
       <c r="C205" t="n">
         <v>83.59999847412109</v>
@@ -5918,7 +5918,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>66.93302154541016</v>
+        <v>66.93302917480469</v>
       </c>
       <c r="C206" t="n">
         <v>74.62999725341797</v>
@@ -5947,7 +5947,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>64.11582946777344</v>
+        <v>64.11581420898438</v>
       </c>
       <c r="C207" t="n">
         <v>71.02999877929688</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>66.73484039306641</v>
+        <v>66.73483276367188</v>
       </c>
       <c r="C210" t="n">
         <v>73.45999908447266</v>
@@ -6063,7 +6063,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>67.40709686279297</v>
+        <v>67.40708923339844</v>
       </c>
       <c r="C211" t="n">
         <v>74.19999694824219</v>
@@ -6121,7 +6121,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>61.1049690246582</v>
+        <v>61.10497665405273</v>
       </c>
       <c r="C213" t="n">
         <v>66.80000305175781</v>
@@ -6150,7 +6150,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>52.4057502746582</v>
+        <v>52.40575408935547</v>
       </c>
       <c r="C214" t="n">
         <v>57.29000091552734</v>
@@ -6179,7 +6179,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>53.32964706420898</v>
+        <v>53.32963943481445</v>
       </c>
       <c r="C215" t="n">
         <v>58.29999923706055</v>
@@ -6208,7 +6208,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>53.95726776123047</v>
+        <v>53.95726013183594</v>
       </c>
       <c r="C216" t="n">
         <v>58.5099983215332</v>
@@ -6237,7 +6237,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>56.01374053955078</v>
+        <v>56.01374435424805</v>
       </c>
       <c r="C217" t="n">
         <v>60.7400016784668</v>
@@ -6266,7 +6266,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>54.06793212890625</v>
+        <v>54.06792449951172</v>
       </c>
       <c r="C218" t="n">
         <v>58.63000106811523</v>
@@ -6295,7 +6295,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>51.3614501953125</v>
+        <v>51.36145401000977</v>
       </c>
       <c r="C219" t="n">
         <v>55.18999862670898</v>
@@ -6353,7 +6353,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>62.32428359985352</v>
+        <v>62.32426834106445</v>
       </c>
       <c r="C221" t="n">
         <v>66.97000122070312</v>
@@ -6440,7 +6440,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>71.55130004882812</v>
+        <v>71.55129241943359</v>
       </c>
       <c r="C224" t="n">
         <v>76.38999938964844</v>
@@ -6498,7 +6498,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>79.68849945068359</v>
+        <v>79.68848419189453</v>
       </c>
       <c r="C226" t="n">
         <v>84.52999877929688</v>
@@ -6556,7 +6556,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>74.66116333007812</v>
+        <v>74.66117095947266</v>
       </c>
       <c r="C228" t="n">
         <v>78.66999816894531</v>
@@ -6817,7 +6817,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>70.03720855712891</v>
+        <v>70.03721618652344</v>
       </c>
       <c r="C237" t="n">
         <v>72.05000305175781</v>
@@ -6962,7 +6962,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>86.02300262451172</v>
+        <v>86.02301025390625</v>
       </c>
       <c r="C242" t="n">
         <v>87.90000152587891</v>
@@ -7020,7 +7020,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>91.51644897460938</v>
+        <v>91.51645660400391</v>
       </c>
       <c r="C244" t="n">
         <v>92.87999725341797</v>
